--- a/inasistencias-6A-Tc/Alumnos-6A-TC.xlsx
+++ b/inasistencias-6A-Tc/Alumnos-6A-TC.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -16,6 +16,8 @@
     <sheet name="3-Rl paralelo" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="4-RC paralelo" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="evaluacion" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="7-ctosCombinados" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="8-CtosComb" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="107">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -114,6 +116,9 @@
   </si>
   <si>
     <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T</t>
   </si>
   <si>
     <t xml:space="preserve">Santiago</t>
@@ -311,7 +316,19 @@
     <t xml:space="preserve">valoracion</t>
   </si>
   <si>
-    <t xml:space="preserve">1A-2A</t>
+    <t xml:space="preserve">Grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 -1A-2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-Ctos Comb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-Ctos Comb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8-Ctos Comb</t>
   </si>
   <si>
     <t xml:space="preserve">cañon de Gauss</t>
@@ -463,7 +480,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -504,6 +521,21 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -692,7 +724,7 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="8.68"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="19" min="6" style="1" width="8.75"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="20" style="1" width="13.25"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="23" min="21" style="1" width="8.75"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="29" min="21" style="1" width="8.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16200" style="1" width="10.58"/>
   </cols>
   <sheetData>
@@ -803,13 +835,27 @@
       <c r="AH2" s="3" t="n">
         <v>46192</v>
       </c>
-      <c r="AI2" s="3"/>
-      <c r="AJ2" s="3"/>
-      <c r="AK2" s="3"/>
-      <c r="AL2" s="3"/>
-      <c r="AM2" s="3"/>
-      <c r="AN2" s="3"/>
-      <c r="AO2" s="3"/>
+      <c r="AI2" s="3" t="n">
+        <v>46199</v>
+      </c>
+      <c r="AJ2" s="3" t="n">
+        <v>46180</v>
+      </c>
+      <c r="AK2" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="AL2" s="3" t="n">
+        <v>46220</v>
+      </c>
+      <c r="AM2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN2" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="AO2" s="3" t="n">
+        <v>46241</v>
+      </c>
       <c r="AP2" s="3"/>
       <c r="AQ2" s="3"/>
       <c r="AR2" s="3"/>
@@ -1664,7 +1710,25 @@
       <c r="AG3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH3" s="5" t="s">
+      <c r="AH3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1765,8 +1829,26 @@
       <c r="AG4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH4" s="5" t="s">
+      <c r="AH4" s="2" t="s">
         <v>18</v>
+      </c>
+      <c r="AI4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO4" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1866,7 +1948,25 @@
       <c r="AG5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH5" s="5" t="s">
+      <c r="AH5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO5" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1967,7 +2067,25 @@
       <c r="AG6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH6" s="5" t="s">
+      <c r="AH6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO6" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2071,7 +2189,28 @@
       <c r="AG7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH7" s="5" t="s">
+      <c r="AH7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AM7" s="6" t="n">
+        <v>0.847222222222222</v>
+      </c>
+      <c r="AN7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO7" s="5" t="s">
         <v>13</v>
       </c>
       <c r="WYB7" s="2"/>
@@ -2265,13 +2404,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>14</v>
@@ -2362,13 +2501,25 @@
       <c r="AH8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AI8" s="1"/>
-      <c r="AJ8" s="1"/>
-      <c r="AK8" s="1"/>
-      <c r="AL8" s="1"/>
+      <c r="AI8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL8" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AM8" s="1"/>
-      <c r="AN8" s="1"/>
-      <c r="AO8" s="1"/>
+      <c r="AN8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO8" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="1"/>
       <c r="AR8" s="1"/>
@@ -2684,13 +2835,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>13</v>
@@ -2776,7 +2927,25 @@
       <c r="AG9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH9" s="5" t="s">
+      <c r="AH9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2785,13 +2954,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>13</v>
@@ -2869,7 +3038,7 @@
         <v>13</v>
       </c>
       <c r="AE10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AF10" s="2" t="s">
         <v>13</v>
@@ -2877,7 +3046,25 @@
       <c r="AG10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH10" s="5" t="s">
+      <c r="AH10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO10" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2886,13 +3073,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>13</v>
@@ -2978,7 +3165,25 @@
       <c r="AG11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AH11" s="5" t="s">
+      <c r="AH11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="WYB11" s="2"/>
@@ -3172,13 +3377,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>13</v>
@@ -3269,13 +3474,25 @@
       <c r="AH12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AI12" s="1"/>
-      <c r="AJ12" s="1"/>
-      <c r="AK12" s="1"/>
-      <c r="AL12" s="1"/>
+      <c r="AI12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL12" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AM12" s="1"/>
-      <c r="AN12" s="1"/>
-      <c r="AO12" s="1"/>
+      <c r="AN12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO12" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AP12" s="1"/>
       <c r="AQ12" s="1"/>
       <c r="AR12" s="1"/>
@@ -3591,13 +3808,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>13</v>
@@ -3685,19 +3902,37 @@
       <c r="AH13" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AI13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO13" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>13</v>
@@ -3785,19 +4020,37 @@
       <c r="AH14" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AI14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO14" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>13</v>
@@ -3888,13 +4141,25 @@
       <c r="AH15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AI15" s="1"/>
-      <c r="AJ15" s="1"/>
-      <c r="AK15" s="1"/>
-      <c r="AL15" s="1"/>
+      <c r="AI15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL15" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="AM15" s="1"/>
-      <c r="AN15" s="1"/>
-      <c r="AO15" s="1"/>
+      <c r="AN15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO15" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AP15" s="1"/>
       <c r="AQ15" s="1"/>
       <c r="AR15" s="1"/>
@@ -4210,13 +4475,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>13</v>
@@ -4264,7 +4529,7 @@
         <v>13</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="W16" s="1" t="s">
         <v>13</v>
@@ -4305,6 +4570,24 @@
         <v>13</v>
       </c>
       <c r="AH16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="WYB16" s="2"/>
@@ -4498,13 +4781,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>13</v>
@@ -4590,6 +4873,24 @@
         <v>13</v>
       </c>
       <c r="AH17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO17" s="1" t="s">
         <v>13</v>
       </c>
       <c r="WYB17" s="2"/>
@@ -4783,13 +5084,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>13</v>
@@ -4880,13 +5181,27 @@
       <c r="AH18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AI18" s="1"/>
-      <c r="AJ18" s="1"/>
-      <c r="AK18" s="1"/>
-      <c r="AL18" s="1"/>
-      <c r="AM18" s="1"/>
-      <c r="AN18" s="1"/>
-      <c r="AO18" s="1"/>
+      <c r="AI18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AM18" s="6" t="n">
+        <v>0.847222222222222</v>
+      </c>
+      <c r="AN18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO18" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="AP18" s="1"/>
       <c r="AQ18" s="1"/>
       <c r="AR18" s="1"/>
@@ -5202,13 +5517,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>13</v>
@@ -5254,7 +5569,7 @@
         <v>14</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="U19" s="1" t="s">
         <v>13</v>
@@ -5301,13 +5616,27 @@
       <c r="AH19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AI19" s="1"/>
-      <c r="AJ19" s="1"/>
-      <c r="AK19" s="1"/>
-      <c r="AL19" s="1"/>
-      <c r="AM19" s="1"/>
-      <c r="AN19" s="1"/>
-      <c r="AO19" s="1"/>
+      <c r="AI19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AM19" s="6" t="n">
+        <v>0.847222222222222</v>
+      </c>
+      <c r="AN19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO19" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AP19" s="1"/>
       <c r="AQ19" s="1"/>
       <c r="AR19" s="1"/>
@@ -5623,13 +5952,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>13</v>
@@ -5715,6 +6044,24 @@
         <v>13</v>
       </c>
       <c r="AH20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO20" s="1" t="s">
         <v>13</v>
       </c>
       <c r="WYB20" s="2"/>
@@ -5908,13 +6255,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>13</v>
@@ -6002,19 +6349,37 @@
       <c r="AH21" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AI21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO21" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="22" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>14</v>
@@ -6091,7 +6456,7 @@
         <v>13</v>
       </c>
       <c r="AE22" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AF22" s="1" t="s">
         <v>13</v>
@@ -6100,6 +6465,24 @@
         <v>13</v>
       </c>
       <c r="AH22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO22" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6108,13 +6491,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>13</v>
@@ -6205,13 +6588,27 @@
       <c r="AH23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AI23" s="1"/>
-      <c r="AJ23" s="1"/>
-      <c r="AK23" s="1"/>
-      <c r="AL23" s="1"/>
-      <c r="AM23" s="1"/>
-      <c r="AN23" s="1"/>
-      <c r="AO23" s="1"/>
+      <c r="AI23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AM23" s="6" t="n">
+        <v>0.847222222222222</v>
+      </c>
+      <c r="AN23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO23" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AP23" s="1"/>
       <c r="AQ23" s="1"/>
       <c r="AR23" s="1"/>
@@ -6617,10 +7014,34 @@
         <f aca="false">COUNTIF(AH3:AH23,"P")</f>
         <v>21</v>
       </c>
+      <c r="AI24" s="1" t="n">
+        <f aca="false">COUNTIF(AI3:AI23,"P")</f>
+        <v>18</v>
+      </c>
+      <c r="AJ24" s="1" t="n">
+        <f aca="false">COUNTIF(AJ3:AJ23,"P")</f>
+        <v>17</v>
+      </c>
+      <c r="AK24" s="1" t="n">
+        <f aca="false">COUNTIF(AK3:AK23,"P")</f>
+        <v>17</v>
+      </c>
+      <c r="AL24" s="1" t="n">
+        <f aca="false">COUNTIF(AL3:AL23,"P")</f>
+        <v>16</v>
+      </c>
+      <c r="AN24" s="1" t="n">
+        <f aca="false">COUNTIF(AN3:AN23,"P")</f>
+        <v>18</v>
+      </c>
+      <c r="AO24" s="1" t="n">
+        <f aca="false">COUNTIF(AO3:AO23,"P")</f>
+        <v>20</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E25" s="1" t="n">
         <f aca="false">COUNTIF(E3:E23,"M")</f>
@@ -6710,10 +7131,34 @@
         <f aca="false">COUNTIF(AH3:AH23,"M")</f>
         <v>0</v>
       </c>
+      <c r="AI25" s="1" t="n">
+        <f aca="false">COUNTIF(AI3:AI23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="1" t="n">
+        <f aca="false">COUNTIF(AJ3:AJ23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AK25" s="1" t="n">
+        <f aca="false">COUNTIF(AK3:AK23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL25" s="1" t="n">
+        <f aca="false">COUNTIF(AL3:AL23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AN25" s="1" t="n">
+        <f aca="false">COUNTIF(AN3:AN23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AO25" s="1" t="n">
+        <f aca="false">COUNTIF(AO3:AO23,"M")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E26" s="1" t="n">
         <f aca="false">COUNTIF(E3:E23,"T")</f>
@@ -6803,10 +7248,34 @@
         <f aca="false">COUNTIF(AH3:AH23,"T")</f>
         <v>0</v>
       </c>
+      <c r="AI26" s="1" t="n">
+        <f aca="false">COUNTIF(AI3:AI23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="1" t="n">
+        <f aca="false">COUNTIF(AJ3:AJ23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AK26" s="1" t="n">
+        <f aca="false">COUNTIF(AK3:AK23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AL26" s="1" t="n">
+        <f aca="false">COUNTIF(AL3:AL23,"T")</f>
+        <v>4</v>
+      </c>
+      <c r="AN26" s="1" t="n">
+        <f aca="false">COUNTIF(AN3:AN23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AO26" s="1" t="n">
+        <f aca="false">COUNTIF(AO3:AO23,"T")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E27" s="1" t="n">
         <f aca="false">COUNTIF(E3:E23,"O")</f>
@@ -6896,10 +7365,34 @@
         <f aca="false">COUNTIF(AH3:AH23,"O")</f>
         <v>0</v>
       </c>
+      <c r="AI27" s="1" t="n">
+        <f aca="false">COUNTIF(AI3:AI23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="1" t="n">
+        <f aca="false">COUNTIF(AJ3:AJ23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="AK27" s="1" t="n">
+        <f aca="false">COUNTIF(AK3:AK23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="AL27" s="1" t="n">
+        <f aca="false">COUNTIF(AL3:AL23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="AN27" s="1" t="n">
+        <f aca="false">COUNTIF(AN3:AN23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="AO27" s="1" t="n">
+        <f aca="false">COUNTIF(AO3:AO23,"O")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E28" s="1" t="n">
         <f aca="false">SUM(E24:E27)</f>
@@ -6988,6 +7481,30 @@
       <c r="AH28" s="1" t="n">
         <f aca="false">SUM(AH24:AH26)</f>
         <v>21</v>
+      </c>
+      <c r="AI28" s="1" t="n">
+        <f aca="false">SUM(AI24:AI26)</f>
+        <v>18</v>
+      </c>
+      <c r="AJ28" s="1" t="n">
+        <f aca="false">SUM(AJ24:AJ26)</f>
+        <v>17</v>
+      </c>
+      <c r="AK28" s="1" t="n">
+        <f aca="false">SUM(AK24:AK26)</f>
+        <v>17</v>
+      </c>
+      <c r="AL28" s="1" t="n">
+        <f aca="false">SUM(AL24:AL26)</f>
+        <v>20</v>
+      </c>
+      <c r="AN28" s="1" t="n">
+        <f aca="false">SUM(AN24:AN26)</f>
+        <v>18</v>
+      </c>
+      <c r="AO28" s="1" t="n">
+        <f aca="false">SUM(AO24:AO26)</f>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -7013,6 +7530,331 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="19.94"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -7025,9 +7867,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="8" min="3" style="1" width="9.6"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="9" style="1" width="12.8"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="12" min="11" style="1" width="9.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="976" min="976" style="1" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16334" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="13" min="11" style="1" width="9.6"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="15" min="14" style="0" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="0" width="16.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="16.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="980" min="980" style="1" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16338" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7041,49 +7886,61 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7130,7 +7987,13 @@
         <f aca="false">IF(N3&gt;6,"TEA",IF(N3&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="P3" s="1" t="n">
+      <c r="Q3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7174,6 +8037,12 @@
         <f aca="false">IF(N4&gt;6,"TEA",IF(N4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="S4" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -7194,9 +8063,11 @@
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>46220</v>
+      </c>
       <c r="J5" s="4" t="n">
         <v>8</v>
       </c>
@@ -7209,13 +8080,19 @@
       </c>
       <c r="N5" s="4" t="n">
         <f aca="false">ROUND(AVERAGE(C5,D5,F5,H5,J5,L5,M4),0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O5" s="4" t="str">
         <f aca="false">IF(N5&gt;6,"TEA",IF(N5&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
-      </c>
-      <c r="P5" s="1" t="n">
+        <v>TEA</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7259,7 +8136,13 @@
         <f aca="false">IF(N6&gt;6,"TEA",IF(N6&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="Q6" s="1" t="n">
+      <c r="S6" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" s="1" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7303,11 +8186,12 @@
         <f aca="false">IF(N7&gt;6,"TEA",IF(N7&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="XDH7" s="2"/>
-      <c r="XDI7" s="2"/>
-      <c r="XDJ7" s="2"/>
-      <c r="XDK7" s="2"/>
-      <c r="XDL7" s="2"/>
+      <c r="S7" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="T7" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="XDM7" s="2"/>
       <c r="XDN7" s="2"/>
       <c r="XDO7" s="2"/>
@@ -7351,14 +8235,13 @@
       <c r="XFA7" s="2"/>
       <c r="XFB7" s="2"/>
       <c r="XFC7" s="2"/>
-      <c r="XFD7" s="2"/>
     </row>
     <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>5</v>
@@ -7377,9 +8260,11 @@
         <v>9</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" s="4"/>
+        <v>9</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>46171</v>
+      </c>
       <c r="L8" s="4" t="n">
         <v>9</v>
       </c>
@@ -7388,22 +8273,26 @@
       </c>
       <c r="N8" s="4" t="n">
         <f aca="false">ROUND(AVERAGE(C8,D8,F8,H8,J8,L8,M7),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O8" s="4" t="str">
         <f aca="false">IF(N8&gt;6,"TEA",IF(N8&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="P8" s="1" t="n">
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="R8" s="1"/>
+      <c r="S8" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="U8" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="AKN8" s="1"/>
-      <c r="AKO8" s="1"/>
-      <c r="AKP8" s="1"/>
-      <c r="AKQ8" s="1"/>
       <c r="AKR8" s="1"/>
       <c r="AKS8" s="1"/>
       <c r="AKT8" s="1"/>
@@ -7455,10 +8344,10 @@
       <c r="AMN8" s="1"/>
       <c r="AMO8" s="1"/>
       <c r="AMP8" s="1"/>
-      <c r="XDF8" s="1"/>
-      <c r="XDG8" s="1"/>
-      <c r="XDH8" s="1"/>
-      <c r="XDI8" s="1"/>
+      <c r="AMQ8" s="1"/>
+      <c r="AMR8" s="1"/>
+      <c r="AMS8" s="1"/>
+      <c r="AMT8" s="1"/>
       <c r="XDJ8" s="1"/>
       <c r="XDK8" s="1"/>
       <c r="XDL8" s="1"/>
@@ -7512,7 +8401,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>9</v>
@@ -7549,13 +8438,19 @@
         <f aca="false">IF(N9&gt;6,"TEA",IF(N9&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="S9" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" s="0" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>10</v>
@@ -7590,13 +8485,19 @@
         <f aca="false">IF(N10&gt;6,"TEA",IF(N10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="S10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>10</v>
@@ -7631,14 +8532,15 @@
         <f aca="false">IF(N11&gt;6,"TEA",IF(N11&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="Q11" s="1" t="n">
+      <c r="S11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="U11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="XDH11" s="2"/>
-      <c r="XDI11" s="2"/>
-      <c r="XDJ11" s="2"/>
-      <c r="XDK11" s="2"/>
-      <c r="XDL11" s="2"/>
       <c r="XDM11" s="2"/>
       <c r="XDN11" s="2"/>
       <c r="XDO11" s="2"/>
@@ -7682,14 +8584,13 @@
       <c r="XFA11" s="2"/>
       <c r="XFB11" s="2"/>
       <c r="XFC11" s="2"/>
-      <c r="XFD11" s="2"/>
     </row>
     <row r="12" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>10</v>
@@ -7722,13 +8623,17 @@
         <f aca="false">IF(N12&gt;6,"TEA",IF(N12&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="P12" s="1" t="n">
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AKN12" s="1"/>
-      <c r="AKO12" s="1"/>
-      <c r="AKP12" s="1"/>
-      <c r="AKQ12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="AKR12" s="1"/>
       <c r="AKS12" s="1"/>
       <c r="AKT12" s="1"/>
@@ -7780,10 +8685,10 @@
       <c r="AMN12" s="1"/>
       <c r="AMO12" s="1"/>
       <c r="AMP12" s="1"/>
-      <c r="XDF12" s="1"/>
-      <c r="XDG12" s="1"/>
-      <c r="XDH12" s="1"/>
-      <c r="XDI12" s="1"/>
+      <c r="AMQ12" s="1"/>
+      <c r="AMR12" s="1"/>
+      <c r="AMS12" s="1"/>
+      <c r="AMT12" s="1"/>
       <c r="XDJ12" s="1"/>
       <c r="XDK12" s="1"/>
       <c r="XDL12" s="1"/>
@@ -7837,7 +8742,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>10</v>
@@ -7874,13 +8779,19 @@
         <f aca="false">IF(N13&gt;6,"TEA",IF(N13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="S13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" s="0" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>10</v>
@@ -7915,13 +8826,19 @@
         <f aca="false">IF(N14&gt;6,"TEA",IF(N14&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="S14" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="T14" s="0" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>8</v>
@@ -7954,13 +8871,17 @@
         <f aca="false">IF(N15&gt;6,"TEA",IF(N15&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="P15" s="1" t="n">
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AKN15" s="1"/>
-      <c r="AKO15" s="1"/>
-      <c r="AKP15" s="1"/>
-      <c r="AKQ15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" s="0" t="n">
+        <v>3</v>
+      </c>
       <c r="AKR15" s="1"/>
       <c r="AKS15" s="1"/>
       <c r="AKT15" s="1"/>
@@ -8012,10 +8933,10 @@
       <c r="AMN15" s="1"/>
       <c r="AMO15" s="1"/>
       <c r="AMP15" s="1"/>
-      <c r="XDF15" s="1"/>
-      <c r="XDG15" s="1"/>
-      <c r="XDH15" s="1"/>
-      <c r="XDI15" s="1"/>
+      <c r="AMQ15" s="1"/>
+      <c r="AMR15" s="1"/>
+      <c r="AMS15" s="1"/>
+      <c r="AMT15" s="1"/>
       <c r="XDJ15" s="1"/>
       <c r="XDK15" s="1"/>
       <c r="XDL15" s="1"/>
@@ -8069,7 +8990,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>10</v>
@@ -8104,11 +9025,12 @@
         <f aca="false">IF(N16&gt;6,"TEA",IF(N16&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="XDH16" s="2"/>
-      <c r="XDI16" s="2"/>
-      <c r="XDJ16" s="2"/>
-      <c r="XDK16" s="2"/>
-      <c r="XDL16" s="2"/>
+      <c r="S16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" s="0" t="n">
+        <v>8</v>
+      </c>
       <c r="XDM16" s="2"/>
       <c r="XDN16" s="2"/>
       <c r="XDO16" s="2"/>
@@ -8152,14 +9074,13 @@
       <c r="XFA16" s="2"/>
       <c r="XFB16" s="2"/>
       <c r="XFC16" s="2"/>
-      <c r="XFD16" s="2"/>
     </row>
     <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>10</v>
@@ -8194,14 +9115,15 @@
         <f aca="false">IF(N17&gt;6,"TEA",IF(N17&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="P17" s="1" t="n">
+      <c r="Q17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="XDH17" s="2"/>
-      <c r="XDI17" s="2"/>
-      <c r="XDJ17" s="2"/>
-      <c r="XDK17" s="2"/>
-      <c r="XDL17" s="2"/>
+      <c r="S17" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="T17" s="0" t="n">
+        <v>9</v>
+      </c>
       <c r="XDM17" s="2"/>
       <c r="XDN17" s="2"/>
       <c r="XDO17" s="2"/>
@@ -8245,14 +9167,13 @@
       <c r="XFA17" s="2"/>
       <c r="XFB17" s="2"/>
       <c r="XFC17" s="2"/>
-      <c r="XFD17" s="2"/>
     </row>
     <row r="18" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>5</v>
@@ -8261,9 +9182,11 @@
         <v>8</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>46220</v>
+      </c>
       <c r="H18" s="2" t="n">
         <v>8</v>
       </c>
@@ -8285,13 +9208,17 @@
         <f aca="false">IF(N18&gt;6,"TEA",IF(N18&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
-      <c r="P18" s="1" t="n">
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AKN18" s="1"/>
-      <c r="AKO18" s="1"/>
-      <c r="AKP18" s="1"/>
-      <c r="AKQ18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="0" t="n">
+        <v>6</v>
+      </c>
       <c r="AKR18" s="1"/>
       <c r="AKS18" s="1"/>
       <c r="AKT18" s="1"/>
@@ -8343,10 +9270,10 @@
       <c r="AMN18" s="1"/>
       <c r="AMO18" s="1"/>
       <c r="AMP18" s="1"/>
-      <c r="XDF18" s="1"/>
-      <c r="XDG18" s="1"/>
-      <c r="XDH18" s="1"/>
-      <c r="XDI18" s="1"/>
+      <c r="AMQ18" s="1"/>
+      <c r="AMR18" s="1"/>
+      <c r="AMS18" s="1"/>
+      <c r="AMT18" s="1"/>
       <c r="XDJ18" s="1"/>
       <c r="XDK18" s="1"/>
       <c r="XDL18" s="1"/>
@@ -8400,10 +9327,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>8</v>
@@ -8428,19 +9355,23 @@
       </c>
       <c r="N19" s="4" t="n">
         <f aca="false">ROUND(AVERAGE(C19,D19,F19,H19,J19,L19,M18),0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O19" s="4" t="str">
         <f aca="false">IF(N19&gt;6,"TEA",IF(N19&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
-      </c>
-      <c r="P19" s="1" t="n">
+        <v>TEA</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AKN19" s="1"/>
-      <c r="AKO19" s="1"/>
-      <c r="AKP19" s="1"/>
-      <c r="AKQ19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="T19" s="0" t="n">
+        <v>8</v>
+      </c>
       <c r="AKR19" s="1"/>
       <c r="AKS19" s="1"/>
       <c r="AKT19" s="1"/>
@@ -8492,10 +9423,10 @@
       <c r="AMN19" s="1"/>
       <c r="AMO19" s="1"/>
       <c r="AMP19" s="1"/>
-      <c r="XDF19" s="1"/>
-      <c r="XDG19" s="1"/>
-      <c r="XDH19" s="1"/>
-      <c r="XDI19" s="1"/>
+      <c r="AMQ19" s="1"/>
+      <c r="AMR19" s="1"/>
+      <c r="AMS19" s="1"/>
+      <c r="AMT19" s="1"/>
       <c r="XDJ19" s="1"/>
       <c r="XDK19" s="1"/>
       <c r="XDL19" s="1"/>
@@ -8549,7 +9480,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>10</v>
@@ -8584,14 +9515,15 @@
         <f aca="false">IF(N20&gt;6,"TEA",IF(N20&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="P20" s="1" t="n">
+      <c r="Q20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="XDH20" s="2"/>
-      <c r="XDI20" s="2"/>
-      <c r="XDJ20" s="2"/>
-      <c r="XDK20" s="2"/>
-      <c r="XDL20" s="2"/>
+      <c r="S20" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="T20" s="0" t="n">
+        <v>6</v>
+      </c>
       <c r="XDM20" s="2"/>
       <c r="XDN20" s="2"/>
       <c r="XDO20" s="2"/>
@@ -8635,14 +9567,13 @@
       <c r="XFA20" s="2"/>
       <c r="XFB20" s="2"/>
       <c r="XFC20" s="2"/>
-      <c r="XFD20" s="2"/>
     </row>
     <row r="21" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>10</v>
@@ -8679,7 +9610,13 @@
         <f aca="false">IF(N21&gt;6,"TEA",IF(N21&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="P21" s="1" t="n">
+      <c r="Q21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8688,7 +9625,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>10</v>
@@ -8728,8 +9665,12 @@
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
+      <c r="S22" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" s="0" t="n">
+        <v>6</v>
+      </c>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
@@ -9740,10 +10681,10 @@
       <c r="AMN22" s="1"/>
       <c r="AMO22" s="1"/>
       <c r="AMP22" s="1"/>
-      <c r="XDF22" s="1"/>
-      <c r="XDG22" s="1"/>
-      <c r="XDH22" s="1"/>
-      <c r="XDI22" s="1"/>
+      <c r="AMQ22" s="1"/>
+      <c r="AMR22" s="1"/>
+      <c r="AMS22" s="1"/>
+      <c r="AMT22" s="1"/>
       <c r="XDJ22" s="1"/>
       <c r="XDK22" s="1"/>
       <c r="XDL22" s="1"/>
@@ -9797,7 +10738,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>5</v>
@@ -9834,13 +10775,15 @@
         <f aca="false">IF(N23&gt;6,"TEA",IF(N23&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="P23" s="1" t="n">
+      <c r="Q23" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
+      <c r="S23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" s="0" t="n">
+        <v>7</v>
+      </c>
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
       <c r="W23" s="2"/>
@@ -10796,6 +11739,10 @@
       <c r="AKK23" s="2"/>
       <c r="AKL23" s="2"/>
       <c r="AKM23" s="2"/>
+      <c r="AKN23" s="2"/>
+      <c r="AKO23" s="2"/>
+      <c r="AKP23" s="2"/>
+      <c r="AKQ23" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="N3:O23 C3:L23">
@@ -11082,43 +12029,43 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11166,7 +12113,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1"/>
       <c r="F7" s="2"/>
@@ -11176,7 +12123,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1"/>
       <c r="F8" s="2"/>
@@ -11186,7 +12133,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="1"/>
       <c r="E9" s="1"/>
@@ -11197,7 +12144,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -11206,7 +12153,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -11215,7 +12162,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" s="1"/>
       <c r="E12" s="1"/>
@@ -11226,7 +12173,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -11235,7 +12182,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" s="1"/>
       <c r="E14" s="1"/>
@@ -11246,7 +12193,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15" s="1"/>
@@ -11257,7 +12204,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" s="1"/>
       <c r="F16" s="2"/>
@@ -11267,7 +12214,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -11276,7 +12223,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="2"/>
@@ -11286,7 +12233,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="2"/>
@@ -11296,7 +12243,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F20" s="2"/>
     </row>
@@ -11305,7 +12252,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="2"/>
@@ -11315,7 +12262,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="2"/>
@@ -11325,7 +12272,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -11363,16 +12310,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11529,7 +12476,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>1</v>
@@ -11543,10 +12490,10 @@
         <v>7</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>7</v>
@@ -11565,7 +12512,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>6</v>
@@ -11573,7 +12520,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>5</v>
@@ -11584,10 +12531,10 @@
         <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>10</v>
@@ -11606,7 +12553,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>7</v>
@@ -11614,7 +12561,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>7</v>
@@ -11625,10 +12572,10 @@
         <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>9</v>
@@ -11642,10 +12589,10 @@
         <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>10</v>
@@ -11659,10 +12606,10 @@
         <v>11</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>9</v>
@@ -11681,7 +12628,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>7</v>
@@ -11689,7 +12636,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>7</v>
@@ -11697,7 +12644,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>5</v>
@@ -11708,10 +12655,10 @@
         <v>12</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>9</v>
@@ -11725,10 +12672,10 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>10</v>
@@ -11742,10 +12689,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>6</v>
@@ -11764,7 +12711,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>5</v>
@@ -11772,7 +12719,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>3</v>
@@ -11780,7 +12727,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>2</v>
@@ -11791,10 +12738,10 @@
         <v>15</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>9</v>
@@ -11813,7 +12760,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>7</v>
@@ -11821,7 +12768,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C33" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>5</v>
@@ -11832,10 +12779,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>10</v>
@@ -11854,7 +12801,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C35" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>10</v>
@@ -11862,7 +12809,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C36" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>3</v>
@@ -11873,10 +12820,10 @@
         <v>17</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>9</v>
@@ -11895,7 +12842,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C38" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>8</v>
@@ -11903,7 +12850,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C39" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>3</v>
@@ -11914,10 +12861,10 @@
         <v>18</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>8</v>
@@ -11931,10 +12878,10 @@
         <v>19</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>10</v>
@@ -11948,7 +12895,7 @@
         <v>20</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>1</v>
@@ -11962,10 +12909,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>9</v>
@@ -11984,7 +12931,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C44" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D44" s="1" t="n">
         <v>5</v>
@@ -11992,7 +12939,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C45" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>4</v>
@@ -12000,7 +12947,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C46" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>4</v>
@@ -12008,7 +12955,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C47" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>3</v>
@@ -12016,7 +12963,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C48" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>3</v>
@@ -12024,7 +12971,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C49" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>2</v>
@@ -12085,7 +13032,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12160,10 +13107,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>10</v>
@@ -12174,10 +13121,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>10</v>
@@ -12188,10 +13135,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>10</v>
@@ -12202,10 +13149,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>9</v>
@@ -12216,10 +13163,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>9</v>
@@ -12230,7 +13177,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>1</v>
@@ -12241,10 +13188,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>10</v>
@@ -12255,10 +13202,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>1</v>
@@ -12269,10 +13216,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>6</v>
@@ -12283,10 +13230,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>10</v>
@@ -12297,7 +13244,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>1</v>
@@ -12308,10 +13255,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>9</v>
@@ -12322,7 +13269,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>1</v>
@@ -12333,7 +13280,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>1</v>
@@ -12344,10 +13291,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>10</v>
@@ -12358,10 +13305,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>8</v>
@@ -12413,16 +13360,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12509,10 +13456,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>9</v>
@@ -12526,10 +13473,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>8</v>
@@ -12543,10 +13490,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>9</v>
@@ -12560,10 +13507,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>10</v>
@@ -12577,10 +13524,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>10</v>
@@ -12594,10 +13541,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>10</v>
@@ -12616,7 +13563,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>9</v>
@@ -12624,7 +13571,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>7</v>
@@ -12632,7 +13579,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>6</v>
@@ -12640,7 +13587,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>5</v>
@@ -12651,10 +13598,10 @@
         <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>9</v>
@@ -12668,10 +13615,10 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>5</v>
@@ -12690,7 +13637,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>4</v>
@@ -12701,10 +13648,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>8</v>
@@ -12718,10 +13665,10 @@
         <v>15</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>9</v>
@@ -12735,10 +13682,10 @@
         <v>16</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>8</v>
@@ -12752,10 +13699,10 @@
         <v>17</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>7</v>
@@ -12769,10 +13716,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>9</v>
@@ -12786,10 +13733,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>8</v>
@@ -12803,7 +13750,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>1</v>
@@ -12817,7 +13764,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>1</v>
@@ -12869,16 +13816,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12995,10 +13942,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>6</v>
@@ -13012,7 +13959,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>1</v>
@@ -13026,10 +13973,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>9</v>
@@ -13043,10 +13990,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>9</v>
@@ -13060,10 +14007,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>8</v>
@@ -13077,10 +14024,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>10</v>
@@ -13094,10 +14041,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>10</v>
@@ -13111,10 +14058,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>8</v>
@@ -13128,10 +14075,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>10</v>
@@ -13145,10 +14092,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>9</v>
@@ -13162,7 +14109,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>1</v>
@@ -13176,10 +14123,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>10</v>
@@ -13193,10 +14140,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>9</v>
@@ -13210,10 +14157,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>9</v>
@@ -13227,10 +14174,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>9</v>
@@ -13244,10 +14191,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>8</v>
@@ -13299,7 +14246,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13377,10 +14324,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>10</v>
@@ -13391,10 +14338,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>8.04</v>
@@ -13405,10 +14352,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>9.22</v>
@@ -13419,10 +14366,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>9.02</v>
@@ -13433,10 +14380,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>9.22</v>
@@ -13447,10 +14394,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>9.22</v>
@@ -13461,10 +14408,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>9.12</v>
@@ -13475,10 +14422,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>10</v>
@@ -13489,10 +14436,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>10</v>
@@ -13503,10 +14450,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>9.22</v>
@@ -13517,7 +14464,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>1</v>
@@ -13528,10 +14475,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>9.22</v>
@@ -13542,10 +14489,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>8.04</v>
@@ -13556,10 +14503,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>8.43</v>
@@ -13570,10 +14517,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>8.82</v>
@@ -13584,15 +14531,332 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>6.86</v>
       </c>
     </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D1048576"/>
+  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="19.94"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/inasistencias-6A-Tc/Alumnos-6A-TC.xlsx
+++ b/inasistencias-6A-Tc/Alumnos-6A-TC.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="108">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t xml:space="preserve">morenabonitafacturas@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pendiente</t>
   </si>
   <si>
     <t xml:space="preserve">Pedro Gabriel</t>
@@ -480,7 +483,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="3">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -521,21 +524,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFCC0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -856,7 +844,9 @@
       <c r="AO2" s="3" t="n">
         <v>46241</v>
       </c>
-      <c r="AP2" s="3"/>
+      <c r="AP2" s="3" t="n">
+        <v>46227</v>
+      </c>
       <c r="AQ2" s="3"/>
       <c r="AR2" s="3"/>
       <c r="AS2" s="3"/>
@@ -1728,7 +1718,10 @@
       <c r="AN3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AO3" s="5" t="s">
+      <c r="AO3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1847,7 +1840,10 @@
       <c r="AN4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AO4" s="5" t="s">
+      <c r="AO4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP4" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1966,7 +1962,10 @@
       <c r="AN5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AO5" s="5" t="s">
+      <c r="AO5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP5" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2085,7 +2084,10 @@
       <c r="AN6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="AO6" s="5" t="s">
+      <c r="AO6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP6" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2210,8 +2212,11 @@
       <c r="AN7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>13</v>
+      <c r="AO7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP7" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="WYB7" s="2"/>
       <c r="WYC7" s="2"/>
@@ -2520,7 +2525,9 @@
       <c r="AO8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AP8" s="1"/>
+      <c r="AP8" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="AQ8" s="1"/>
       <c r="AR8" s="1"/>
       <c r="AS8" s="1"/>
@@ -2945,7 +2952,10 @@
       <c r="AN9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AO9" s="5" t="s">
+      <c r="AO9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3064,7 +3074,10 @@
       <c r="AN10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AO10" s="5" t="s">
+      <c r="AO10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP10" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3183,7 +3196,10 @@
       <c r="AN11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AO11" s="5" t="s">
+      <c r="AO11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="WYB11" s="2"/>
@@ -3493,7 +3509,9 @@
       <c r="AO12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AP12" s="1"/>
+      <c r="AP12" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AQ12" s="1"/>
       <c r="AR12" s="1"/>
       <c r="AS12" s="1"/>
@@ -3920,19 +3938,25 @@
       <c r="AO13" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AP13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AQ13" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>13</v>
@@ -4038,19 +4062,22 @@
       <c r="AO14" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AP14" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>13</v>
@@ -4160,7 +4187,9 @@
       <c r="AO15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AP15" s="1"/>
+      <c r="AP15" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AQ15" s="1"/>
       <c r="AR15" s="1"/>
       <c r="AS15" s="1"/>
@@ -4475,13 +4504,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>13</v>
@@ -4529,7 +4558,7 @@
         <v>13</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W16" s="1" t="s">
         <v>13</v>
@@ -4588,6 +4617,9 @@
         <v>13</v>
       </c>
       <c r="AO16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="WYB16" s="2"/>
@@ -4781,13 +4813,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>13</v>
@@ -4891,6 +4923,9 @@
         <v>13</v>
       </c>
       <c r="AO17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP17" s="1" t="s">
         <v>13</v>
       </c>
       <c r="WYB17" s="2"/>
@@ -5084,13 +5119,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>13</v>
@@ -5202,7 +5237,9 @@
       <c r="AO18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AP18" s="1"/>
+      <c r="AP18" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="AQ18" s="1"/>
       <c r="AR18" s="1"/>
       <c r="AS18" s="1"/>
@@ -5517,13 +5554,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>13</v>
@@ -5569,7 +5606,7 @@
         <v>14</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="U19" s="1" t="s">
         <v>13</v>
@@ -5637,7 +5674,9 @@
       <c r="AO19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AP19" s="1"/>
+      <c r="AP19" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="AQ19" s="1"/>
       <c r="AR19" s="1"/>
       <c r="AS19" s="1"/>
@@ -5952,13 +5991,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>13</v>
@@ -6062,6 +6101,9 @@
         <v>13</v>
       </c>
       <c r="AO20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP20" s="1" t="s">
         <v>13</v>
       </c>
       <c r="WYB20" s="2"/>
@@ -6255,13 +6297,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>13</v>
@@ -6367,19 +6409,22 @@
       <c r="AO21" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AP21" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="22" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>14</v>
@@ -6485,19 +6530,22 @@
       <c r="AO22" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AP22" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="23" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>13</v>
@@ -6609,7 +6657,9 @@
       <c r="AO23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AP23" s="1"/>
+      <c r="AP23" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AQ23" s="1"/>
       <c r="AR23" s="1"/>
       <c r="AS23" s="1"/>
@@ -7038,10 +7088,14 @@
         <f aca="false">COUNTIF(AO3:AO23,"P")</f>
         <v>20</v>
       </c>
+      <c r="AP24" s="1" t="n">
+        <f aca="false">COUNTIF(AP3:AP23,"P")</f>
+        <v>17</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E25" s="1" t="n">
         <f aca="false">COUNTIF(E3:E23,"M")</f>
@@ -7155,10 +7209,14 @@
         <f aca="false">COUNTIF(AO3:AO23,"M")</f>
         <v>0</v>
       </c>
+      <c r="AP25" s="1" t="n">
+        <f aca="false">COUNTIF(AP3:AP23,"M")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E26" s="1" t="n">
         <f aca="false">COUNTIF(E3:E23,"T")</f>
@@ -7272,10 +7330,14 @@
         <f aca="false">COUNTIF(AO3:AO23,"T")</f>
         <v>0</v>
       </c>
+      <c r="AP26" s="1" t="n">
+        <f aca="false">COUNTIF(AP3:AP23,"T")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E27" s="1" t="n">
         <f aca="false">COUNTIF(E3:E23,"O")</f>
@@ -7389,10 +7451,14 @@
         <f aca="false">COUNTIF(AO3:AO23,"O")</f>
         <v>0</v>
       </c>
+      <c r="AP27" s="1" t="n">
+        <f aca="false">COUNTIF(AP3:AP23,"O")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E28" s="1" t="n">
         <f aca="false">SUM(E24:E27)</f>
@@ -7505,6 +7571,10 @@
       <c r="AO28" s="1" t="n">
         <f aca="false">SUM(AO24:AO26)</f>
         <v>20</v>
+      </c>
+      <c r="AP28" s="1" t="n">
+        <f aca="false">SUM(AP24:AP26)</f>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -7538,8 +7608,8 @@
   <dimension ref="A1:D22"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="19.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="19.94"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7549,11 +7619,11 @@
       <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
-        <v>102</v>
+      <c r="D1" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7563,10 +7633,10 @@
       <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7577,10 +7647,10 @@
       <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7591,7 +7661,7 @@
       <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7602,10 +7672,10 @@
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7616,7 +7686,7 @@
       <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7627,10 +7697,10 @@
       <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7641,10 +7711,10 @@
       <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7655,10 +7725,10 @@
       <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7669,10 +7739,10 @@
       <c r="B10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7683,10 +7753,10 @@
       <c r="B11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7697,10 +7767,10 @@
       <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7709,12 +7779,12 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7723,12 +7793,12 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7737,12 +7807,12 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7751,12 +7821,12 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7765,12 +7835,12 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7779,12 +7849,12 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7793,12 +7863,12 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7807,12 +7877,12 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="D20" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7821,12 +7891,12 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7835,12 +7905,12 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="1" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7867,10 +7937,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="8" min="3" style="1" width="9.6"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="9" style="1" width="12.8"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="13" min="11" style="1" width="9.6"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="15" min="14" style="0" width="9.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="0" width="16.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="16.46"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="15" min="11" style="1" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="19" style="1" width="16.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="980" min="980" style="1" width="9.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16338" style="1" width="10.58"/>
   </cols>
@@ -7886,61 +7954,61 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7990,10 +8058,10 @@
       <c r="Q3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S3" s="0" t="n">
+      <c r="S3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T3" s="0" t="n">
+      <c r="T3" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8037,10 +8105,10 @@
         <f aca="false">IF(N4&gt;6,"TEA",IF(N4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="S4" s="0" t="n">
+      <c r="S4" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="T4" s="0" t="n">
+      <c r="T4" s="1" t="n">
         <v>7</v>
       </c>
     </row>
@@ -8089,10 +8157,10 @@
       <c r="Q5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S5" s="0" t="n">
+      <c r="S5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="0" t="n">
+      <c r="T5" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8136,10 +8204,10 @@
         <f aca="false">IF(N6&gt;6,"TEA",IF(N6&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="S6" s="0" t="n">
+      <c r="S6" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T6" s="0" t="n">
+      <c r="T6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="U6" s="1" t="n">
@@ -8186,10 +8254,10 @@
         <f aca="false">IF(N7&gt;6,"TEA",IF(N7&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="S7" s="0" t="n">
+      <c r="S7" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="T7" s="0" t="n">
+      <c r="T7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="XDM7" s="2"/>
@@ -8284,10 +8352,10 @@
         <v>1</v>
       </c>
       <c r="R8" s="1"/>
-      <c r="S8" s="0" t="n">
+      <c r="S8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T8" s="0" t="n">
+      <c r="T8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="U8" s="2" t="n">
@@ -8438,10 +8506,10 @@
         <f aca="false">IF(N9&gt;6,"TEA",IF(N9&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="S9" s="0" t="n">
+      <c r="S9" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T9" s="0" t="n">
+      <c r="T9" s="1" t="n">
         <v>8</v>
       </c>
     </row>
@@ -8485,10 +8553,10 @@
         <f aca="false">IF(N10&gt;6,"TEA",IF(N10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="S10" s="0" t="n">
+      <c r="S10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="0" t="n">
+      <c r="T10" s="1" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8532,10 +8600,10 @@
         <f aca="false">IF(N11&gt;6,"TEA",IF(N11&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="S11" s="0" t="n">
+      <c r="S11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T11" s="0" t="n">
+      <c r="T11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="U11" s="1" t="n">
@@ -8628,10 +8696,10 @@
         <v>1</v>
       </c>
       <c r="R12" s="1"/>
-      <c r="S12" s="0" t="n">
+      <c r="S12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T12" s="0" t="n">
+      <c r="T12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AKR12" s="1"/>
@@ -8779,10 +8847,10 @@
         <f aca="false">IF(N13&gt;6,"TEA",IF(N13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="S13" s="0" t="n">
+      <c r="S13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T13" s="0" t="n">
+      <c r="T13" s="1" t="n">
         <v>10</v>
       </c>
     </row>
@@ -8791,7 +8859,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>10</v>
@@ -8826,10 +8894,10 @@
         <f aca="false">IF(N14&gt;6,"TEA",IF(N14&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="S14" s="0" t="n">
+      <c r="S14" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="T14" s="0" t="n">
+      <c r="T14" s="1" t="n">
         <v>8</v>
       </c>
     </row>
@@ -8838,7 +8906,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>8</v>
@@ -8876,10 +8944,10 @@
         <v>1</v>
       </c>
       <c r="R15" s="1"/>
-      <c r="S15" s="0" t="n">
+      <c r="S15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T15" s="0" t="n">
+      <c r="T15" s="1" t="n">
         <v>3</v>
       </c>
       <c r="AKR15" s="1"/>
@@ -8990,7 +9058,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>10</v>
@@ -9025,10 +9093,10 @@
         <f aca="false">IF(N16&gt;6,"TEA",IF(N16&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="S16" s="0" t="n">
+      <c r="S16" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T16" s="0" t="n">
+      <c r="T16" s="1" t="n">
         <v>8</v>
       </c>
       <c r="XDM16" s="2"/>
@@ -9080,7 +9148,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>10</v>
@@ -9118,10 +9186,10 @@
       <c r="Q17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S17" s="0" t="n">
+      <c r="S17" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="T17" s="0" t="n">
+      <c r="T17" s="1" t="n">
         <v>9</v>
       </c>
       <c r="XDM17" s="2"/>
@@ -9173,7 +9241,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>5</v>
@@ -9213,10 +9281,10 @@
         <v>1</v>
       </c>
       <c r="R18" s="1"/>
-      <c r="S18" s="0" t="n">
+      <c r="S18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T18" s="0" t="n">
+      <c r="T18" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AKR18" s="1"/>
@@ -9327,7 +9395,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>7</v>
@@ -9366,10 +9434,10 @@
         <v>1</v>
       </c>
       <c r="R19" s="1"/>
-      <c r="S19" s="0" t="n">
+      <c r="S19" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="T19" s="0" t="n">
+      <c r="T19" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AKR19" s="1"/>
@@ -9480,7 +9548,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>10</v>
@@ -9518,10 +9586,10 @@
       <c r="Q20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S20" s="0" t="n">
+      <c r="S20" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="0" t="n">
+      <c r="T20" s="1" t="n">
         <v>6</v>
       </c>
       <c r="XDM20" s="2"/>
@@ -9573,7 +9641,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>10</v>
@@ -9613,10 +9681,10 @@
       <c r="Q21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S21" s="0" t="n">
+      <c r="S21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T21" s="0" t="n">
+      <c r="T21" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9625,7 +9693,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>10</v>
@@ -9665,10 +9733,10 @@
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
-      <c r="S22" s="0" t="n">
+      <c r="S22" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="T22" s="0" t="n">
+      <c r="T22" s="1" t="n">
         <v>6</v>
       </c>
       <c r="U22" s="1"/>
@@ -10738,7 +10806,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>5</v>
@@ -10778,10 +10846,10 @@
       <c r="Q23" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S23" s="0" t="n">
+      <c r="S23" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T23" s="0" t="n">
+      <c r="T23" s="1" t="n">
         <v>7</v>
       </c>
       <c r="U23" s="2"/>
@@ -12029,43 +12097,43 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12173,7 +12241,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -12182,7 +12250,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" s="1"/>
       <c r="E14" s="1"/>
@@ -12193,7 +12261,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15" s="1"/>
@@ -12204,7 +12272,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1"/>
       <c r="F16" s="2"/>
@@ -12214,7 +12282,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F17" s="2"/>
     </row>
@@ -12223,7 +12291,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="2"/>
@@ -12233,7 +12301,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="2"/>
@@ -12243,7 +12311,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F20" s="2"/>
     </row>
@@ -12252,7 +12320,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="2"/>
@@ -12262,7 +12330,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="2"/>
@@ -12272,7 +12340,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F23" s="2"/>
     </row>
@@ -12310,16 +12378,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12655,10 +12723,10 @@
         <v>12</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>9</v>
@@ -12672,10 +12740,10 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>10</v>
@@ -12689,10 +12757,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>6</v>
@@ -12711,7 +12779,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>5</v>
@@ -12719,7 +12787,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>3</v>
@@ -12727,7 +12795,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>2</v>
@@ -12738,10 +12806,10 @@
         <v>15</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>9</v>
@@ -12760,7 +12828,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>7</v>
@@ -12768,7 +12836,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C33" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>5</v>
@@ -12779,10 +12847,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>10</v>
@@ -12801,7 +12869,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C35" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>10</v>
@@ -12809,7 +12877,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C36" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>3</v>
@@ -12820,10 +12888,10 @@
         <v>17</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>9</v>
@@ -12842,7 +12910,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C38" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>8</v>
@@ -12850,7 +12918,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C39" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>3</v>
@@ -12861,10 +12929,10 @@
         <v>18</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>8</v>
@@ -12878,10 +12946,10 @@
         <v>19</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>10</v>
@@ -12895,7 +12963,7 @@
         <v>20</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>1</v>
@@ -12909,10 +12977,10 @@
         <v>21</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>9</v>
@@ -12931,7 +12999,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C44" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D44" s="1" t="n">
         <v>5</v>
@@ -12939,7 +13007,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C45" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>4</v>
@@ -12947,7 +13015,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C46" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>4</v>
@@ -12955,7 +13023,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C47" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>3</v>
@@ -12963,7 +13031,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C48" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>3</v>
@@ -12971,7 +13039,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C49" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>2</v>
@@ -13032,7 +13100,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13188,10 +13256,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>10</v>
@@ -13202,10 +13270,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>1</v>
@@ -13216,10 +13284,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>6</v>
@@ -13230,10 +13298,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>10</v>
@@ -13244,7 +13312,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>1</v>
@@ -13255,10 +13323,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>9</v>
@@ -13269,7 +13337,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>1</v>
@@ -13280,7 +13348,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>1</v>
@@ -13291,10 +13359,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>10</v>
@@ -13305,10 +13373,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>8</v>
@@ -13360,16 +13428,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13598,10 +13666,10 @@
         <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>9</v>
@@ -13615,10 +13683,10 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>5</v>
@@ -13637,7 +13705,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>4</v>
@@ -13648,10 +13716,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>8</v>
@@ -13665,10 +13733,10 @@
         <v>15</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>9</v>
@@ -13682,10 +13750,10 @@
         <v>16</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>8</v>
@@ -13699,10 +13767,10 @@
         <v>17</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>7</v>
@@ -13716,10 +13784,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>9</v>
@@ -13733,10 +13801,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>8</v>
@@ -13750,7 +13818,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>1</v>
@@ -13764,7 +13832,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>1</v>
@@ -13816,16 +13884,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14041,10 +14109,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>10</v>
@@ -14058,10 +14126,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>8</v>
@@ -14075,10 +14143,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>10</v>
@@ -14092,10 +14160,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>9</v>
@@ -14109,7 +14177,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>1</v>
@@ -14123,10 +14191,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>10</v>
@@ -14140,10 +14208,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>9</v>
@@ -14157,10 +14225,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>9</v>
@@ -14174,10 +14242,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>9</v>
@@ -14191,10 +14259,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>8</v>
@@ -14246,7 +14314,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14408,10 +14476,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>9.12</v>
@@ -14422,10 +14490,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>10</v>
@@ -14436,10 +14504,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>10</v>
@@ -14450,10 +14518,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>9.22</v>
@@ -14464,7 +14532,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>1</v>
@@ -14475,10 +14543,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>9.22</v>
@@ -14489,10 +14557,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>8.04</v>
@@ -14503,10 +14571,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>8.43</v>
@@ -14517,10 +14585,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>8.82</v>
@@ -14531,10 +14599,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>6.86</v>
@@ -14559,8 +14627,8 @@
   <dimension ref="A1:D1048576"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="19.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="19.94"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14570,11 +14638,11 @@
       <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
-        <v>102</v>
+      <c r="D1" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14584,7 +14652,7 @@
       <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14595,10 +14663,10 @@
       <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>9</v>
       </c>
     </row>
@@ -14609,10 +14677,10 @@
       <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14623,10 +14691,10 @@
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>10</v>
       </c>
     </row>
@@ -14637,10 +14705,10 @@
       <c r="B6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>9</v>
       </c>
     </row>
@@ -14651,10 +14719,10 @@
       <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14665,10 +14733,10 @@
       <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>5</v>
       </c>
     </row>
@@ -14679,10 +14747,10 @@
       <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>9</v>
       </c>
     </row>
@@ -14693,10 +14761,10 @@
       <c r="B10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>10</v>
       </c>
     </row>
@@ -14707,10 +14775,10 @@
       <c r="B11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14721,10 +14789,10 @@
       <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14733,12 +14801,12 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>9</v>
       </c>
     </row>
@@ -14747,9 +14815,9 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14758,12 +14826,12 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14772,12 +14840,12 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>8</v>
       </c>
     </row>
@@ -14786,9 +14854,9 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="0" t="n">
+        <v>64</v>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14797,12 +14865,12 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="0" t="n">
+        <v>67</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>6</v>
       </c>
     </row>
@@ -14811,12 +14879,12 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>9</v>
       </c>
     </row>
@@ -14825,9 +14893,9 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D20" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14836,12 +14904,12 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="0" t="n">
+        <v>77</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>8</v>
       </c>
     </row>
@@ -14850,9 +14918,9 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="D22" s="1" t="n">
         <v>1</v>
       </c>
     </row>

--- a/inasistencias-6A-Tc/Alumnos-6A-TC.xlsx
+++ b/inasistencias-6A-Tc/Alumnos-6A-TC.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="109">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t xml:space="preserve">cañon de Gauss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evaluacion</t>
   </si>
   <si>
     <t xml:space="preserve">-</t>
@@ -712,7 +715,7 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="8.68"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="19" min="6" style="1" width="8.75"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="20" style="1" width="13.25"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="29" min="21" style="1" width="8.75"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="40" min="21" style="1" width="8.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16200" style="1" width="10.58"/>
   </cols>
   <sheetData>
@@ -847,15 +850,33 @@
       <c r="AP2" s="3" t="n">
         <v>46227</v>
       </c>
-      <c r="AQ2" s="3"/>
-      <c r="AR2" s="3"/>
-      <c r="AS2" s="3"/>
-      <c r="AT2" s="3"/>
-      <c r="AU2" s="3"/>
-      <c r="AV2" s="3"/>
-      <c r="AW2" s="3"/>
-      <c r="AX2" s="3"/>
-      <c r="AY2" s="3"/>
+      <c r="AQ2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR2" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="AS2" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="AT2" s="3" t="n">
+        <v>46269</v>
+      </c>
+      <c r="AU2" s="3" t="n">
+        <v>46272</v>
+      </c>
+      <c r="AV2" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="AW2" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="AX2" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="AY2" s="3" t="n">
+        <v>46297</v>
+      </c>
       <c r="AZ2" s="3"/>
       <c r="BA2" s="3"/>
       <c r="BB2" s="3"/>
@@ -1721,7 +1742,31 @@
       <c r="AO3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AP3" s="5" t="s">
+      <c r="AP3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY3" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1843,7 +1888,31 @@
       <c r="AO4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AP4" s="5" t="s">
+      <c r="AP4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AR4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AV4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY4" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1965,8 +2034,32 @@
       <c r="AO5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AP5" s="5" t="s">
-        <v>13</v>
+      <c r="AP5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AR5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY5" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2087,7 +2180,31 @@
       <c r="AO6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AP6" s="5" t="s">
+      <c r="AP6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AR6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY6" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2215,8 +2332,32 @@
       <c r="AO7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AP7" s="5" t="s">
+      <c r="AP7" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="AR7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AV7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY7" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="WYB7" s="2"/>
       <c r="WYC7" s="2"/>
@@ -2529,14 +2670,30 @@
         <v>14</v>
       </c>
       <c r="AQ8" s="1"/>
-      <c r="AR8" s="1"/>
-      <c r="AS8" s="1"/>
-      <c r="AT8" s="1"/>
-      <c r="AU8" s="1"/>
-      <c r="AV8" s="1"/>
-      <c r="AW8" s="1"/>
-      <c r="AX8" s="1"/>
-      <c r="AY8" s="1"/>
+      <c r="AR8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AY8" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AZ8" s="1"/>
       <c r="BA8" s="1"/>
       <c r="BB8" s="1"/>
@@ -2955,7 +3112,31 @@
       <c r="AO9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AP9" s="5" t="s">
+      <c r="AP9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AR9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3077,8 +3258,32 @@
       <c r="AO10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AP10" s="5" t="s">
-        <v>13</v>
+      <c r="AP10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AR10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY10" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3199,7 +3404,31 @@
       <c r="AO11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AP11" s="5" t="s">
+      <c r="AP11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AR11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="WYB11" s="2"/>
@@ -3513,14 +3742,30 @@
         <v>13</v>
       </c>
       <c r="AQ12" s="1"/>
-      <c r="AR12" s="1"/>
-      <c r="AS12" s="1"/>
-      <c r="AT12" s="1"/>
-      <c r="AU12" s="1"/>
-      <c r="AV12" s="1"/>
-      <c r="AW12" s="1"/>
-      <c r="AX12" s="1"/>
-      <c r="AY12" s="1"/>
+      <c r="AR12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY12" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="AZ12" s="1"/>
       <c r="BA12" s="1"/>
       <c r="BB12" s="1"/>
@@ -3944,6 +4189,30 @@
       <c r="AQ13" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="AR13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY13" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -4065,6 +4334,30 @@
       <c r="AP14" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AR14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AT14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AV14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY14" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -4191,14 +4484,30 @@
         <v>13</v>
       </c>
       <c r="AQ15" s="1"/>
-      <c r="AR15" s="1"/>
-      <c r="AS15" s="1"/>
-      <c r="AT15" s="1"/>
-      <c r="AU15" s="1"/>
-      <c r="AV15" s="1"/>
-      <c r="AW15" s="1"/>
-      <c r="AX15" s="1"/>
-      <c r="AY15" s="1"/>
+      <c r="AR15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AV15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AW15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY15" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AZ15" s="1"/>
       <c r="BA15" s="1"/>
       <c r="BB15" s="1"/>
@@ -4622,6 +4931,30 @@
       <c r="AP16" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AR16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY16" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="WYB16" s="2"/>
       <c r="WYC16" s="2"/>
       <c r="WYD16" s="2"/>
@@ -4928,6 +5261,30 @@
       <c r="AP17" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AR17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY17" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="WYB17" s="2"/>
       <c r="WYC17" s="2"/>
       <c r="WYD17" s="2"/>
@@ -5241,14 +5598,30 @@
         <v>14</v>
       </c>
       <c r="AQ18" s="1"/>
-      <c r="AR18" s="1"/>
-      <c r="AS18" s="1"/>
-      <c r="AT18" s="1"/>
-      <c r="AU18" s="1"/>
-      <c r="AV18" s="1"/>
-      <c r="AW18" s="1"/>
-      <c r="AX18" s="1"/>
-      <c r="AY18" s="1"/>
+      <c r="AR18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AV18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AW18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AX18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AY18" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AZ18" s="1"/>
       <c r="BA18" s="1"/>
       <c r="BB18" s="1"/>
@@ -5678,14 +6051,30 @@
         <v>14</v>
       </c>
       <c r="AQ19" s="1"/>
-      <c r="AR19" s="1"/>
-      <c r="AS19" s="1"/>
-      <c r="AT19" s="1"/>
-      <c r="AU19" s="1"/>
-      <c r="AV19" s="1"/>
-      <c r="AW19" s="1"/>
-      <c r="AX19" s="1"/>
-      <c r="AY19" s="1"/>
+      <c r="AR19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AV19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY19" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AZ19" s="1"/>
       <c r="BA19" s="1"/>
       <c r="BB19" s="1"/>
@@ -6106,6 +6495,30 @@
       <c r="AP20" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AR20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AW20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY20" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="WYB20" s="2"/>
       <c r="WYC20" s="2"/>
       <c r="WYD20" s="2"/>
@@ -6412,6 +6825,30 @@
       <c r="AP21" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AR21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY21" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="22" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
@@ -6533,6 +6970,30 @@
       <c r="AP22" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="AR22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY22" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="23" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
@@ -6661,14 +7122,30 @@
         <v>13</v>
       </c>
       <c r="AQ23" s="1"/>
-      <c r="AR23" s="1"/>
-      <c r="AS23" s="1"/>
-      <c r="AT23" s="1"/>
-      <c r="AU23" s="1"/>
-      <c r="AV23" s="1"/>
-      <c r="AW23" s="1"/>
-      <c r="AX23" s="1"/>
-      <c r="AY23" s="1"/>
+      <c r="AR23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AV23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY23" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="AZ23" s="1"/>
       <c r="BA23" s="1"/>
       <c r="BB23" s="1"/>
@@ -7092,6 +7569,38 @@
         <f aca="false">COUNTIF(AP3:AP23,"P")</f>
         <v>17</v>
       </c>
+      <c r="AR24" s="1" t="n">
+        <f aca="false">COUNTIF(AR3:AR23,"P")</f>
+        <v>20</v>
+      </c>
+      <c r="AS24" s="1" t="n">
+        <f aca="false">COUNTIF(AS3:AS23,"P")</f>
+        <v>20</v>
+      </c>
+      <c r="AT24" s="1" t="n">
+        <f aca="false">COUNTIF(AT3:AT23,"P")</f>
+        <v>20</v>
+      </c>
+      <c r="AU24" s="1" t="n">
+        <f aca="false">COUNTIF(AU3:AU23,"P")</f>
+        <v>16</v>
+      </c>
+      <c r="AV24" s="1" t="n">
+        <f aca="false">COUNTIF(AV3:AV23,"P")</f>
+        <v>19</v>
+      </c>
+      <c r="AW24" s="1" t="n">
+        <f aca="false">COUNTIF(AW3:AW23,"P")</f>
+        <v>20</v>
+      </c>
+      <c r="AX24" s="1" t="n">
+        <f aca="false">COUNTIF(AX3:AX23,"P")</f>
+        <v>19</v>
+      </c>
+      <c r="AY24" s="1" t="n">
+        <f aca="false">COUNTIF(AY3:AY23,"P")</f>
+        <v>16</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
@@ -7213,6 +7722,38 @@
         <f aca="false">COUNTIF(AP3:AP23,"M")</f>
         <v>0</v>
       </c>
+      <c r="AR25" s="1" t="n">
+        <f aca="false">COUNTIF(AR3:AR23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AS25" s="1" t="n">
+        <f aca="false">COUNTIF(AS3:AS23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AT25" s="1" t="n">
+        <f aca="false">COUNTIF(AT3:AT23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AU25" s="1" t="n">
+        <f aca="false">COUNTIF(AU3:AU23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AV25" s="1" t="n">
+        <f aca="false">COUNTIF(AV3:AV23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AW25" s="1" t="n">
+        <f aca="false">COUNTIF(AW3:AW23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AX25" s="1" t="n">
+        <f aca="false">COUNTIF(AX3:AX23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="1" t="n">
+        <f aca="false">COUNTIF(AY3:AY23,"M")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
@@ -7334,6 +7875,38 @@
         <f aca="false">COUNTIF(AP3:AP23,"T")</f>
         <v>0</v>
       </c>
+      <c r="AR26" s="1" t="n">
+        <f aca="false">COUNTIF(AR3:AR23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AS26" s="1" t="n">
+        <f aca="false">COUNTIF(AS3:AS23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AT26" s="1" t="n">
+        <f aca="false">COUNTIF(AT3:AT23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AU26" s="1" t="n">
+        <f aca="false">COUNTIF(AU3:AU23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AV26" s="1" t="n">
+        <f aca="false">COUNTIF(AV3:AV23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AW26" s="1" t="n">
+        <f aca="false">COUNTIF(AW3:AW23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AX26" s="1" t="n">
+        <f aca="false">COUNTIF(AX3:AX23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AY26" s="1" t="n">
+        <f aca="false">COUNTIF(AY3:AY23,"T")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
@@ -7455,6 +8028,38 @@
         <f aca="false">COUNTIF(AP3:AP23,"O")</f>
         <v>0</v>
       </c>
+      <c r="AR27" s="1" t="n">
+        <f aca="false">COUNTIF(AR3:AR23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="AS27" s="1" t="n">
+        <f aca="false">COUNTIF(AS3:AS23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="AT27" s="1" t="n">
+        <f aca="false">COUNTIF(AT3:AT23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="AU27" s="1" t="n">
+        <f aca="false">COUNTIF(AU3:AU23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="AV27" s="1" t="n">
+        <f aca="false">COUNTIF(AV3:AV23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="AW27" s="1" t="n">
+        <f aca="false">COUNTIF(AW3:AW23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="AX27" s="1" t="n">
+        <f aca="false">COUNTIF(AX3:AX23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="AY27" s="1" t="n">
+        <f aca="false">COUNTIF(AY3:AY23,"O")</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
@@ -7575,6 +8180,38 @@
       <c r="AP28" s="1" t="n">
         <f aca="false">SUM(AP24:AP26)</f>
         <v>17</v>
+      </c>
+      <c r="AR28" s="1" t="n">
+        <f aca="false">SUM(AR24:AR26)</f>
+        <v>20</v>
+      </c>
+      <c r="AS28" s="1" t="n">
+        <f aca="false">SUM(AS24:AS26)</f>
+        <v>20</v>
+      </c>
+      <c r="AT28" s="1" t="n">
+        <f aca="false">SUM(AT24:AT26)</f>
+        <v>20</v>
+      </c>
+      <c r="AU28" s="1" t="n">
+        <f aca="false">SUM(AU24:AU26)</f>
+        <v>16</v>
+      </c>
+      <c r="AV28" s="1" t="n">
+        <f aca="false">SUM(AV24:AV26)</f>
+        <v>19</v>
+      </c>
+      <c r="AW28" s="1" t="n">
+        <f aca="false">SUM(AW24:AW26)</f>
+        <v>20</v>
+      </c>
+      <c r="AX28" s="1" t="n">
+        <f aca="false">SUM(AX24:AX26)</f>
+        <v>19</v>
+      </c>
+      <c r="AY28" s="1" t="n">
+        <f aca="false">SUM(AY24:AY26)</f>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -7623,7 +8260,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7937,8 +8574,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="8" min="3" style="1" width="9.6"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="9" style="1" width="12.8"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="15" min="11" style="1" width="9.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="19" style="1" width="16.46"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="18" min="11" style="1" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="19" style="1" width="16.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="16.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="980" min="980" style="1" width="9.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16338" style="1" width="10.58"/>
   </cols>
@@ -8010,6 +8648,9 @@
       <c r="U2" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="V2" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -8064,6 +8705,9 @@
       <c r="T3" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="V3" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -8111,6 +8755,9 @@
       <c r="T4" s="1" t="n">
         <v>7</v>
       </c>
+      <c r="V4" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -8163,6 +8810,9 @@
       <c r="T5" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="V5" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -8213,6 +8863,9 @@
       <c r="U6" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="V6" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -8259,6 +8912,9 @@
       </c>
       <c r="T7" s="1" t="n">
         <v>1</v>
+      </c>
+      <c r="V7" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="XDM7" s="2"/>
       <c r="XDN7" s="2"/>
@@ -8360,6 +9016,9 @@
       </c>
       <c r="U8" s="2" t="n">
         <v>9</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="AKR8" s="1"/>
       <c r="AKS8" s="1"/>
@@ -8512,6 +9171,9 @@
       <c r="T9" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="V9" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -8559,6 +9221,9 @@
       <c r="T10" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="V10" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -8608,6 +9273,9 @@
       </c>
       <c r="U11" s="1" t="n">
         <v>8</v>
+      </c>
+      <c r="V11" s="1" t="n">
+        <v>7</v>
       </c>
       <c r="XDM11" s="2"/>
       <c r="XDN11" s="2"/>
@@ -8701,6 +9369,9 @@
       </c>
       <c r="T12" s="1" t="n">
         <v>1</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="AKR12" s="1"/>
       <c r="AKS12" s="1"/>
@@ -8853,6 +9524,9 @@
       <c r="T13" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="V13" s="1" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -8900,6 +9574,9 @@
       <c r="T14" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="V14" s="1" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -8948,6 +9625,9 @@
         <v>1</v>
       </c>
       <c r="T15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="AKR15" s="1"/>
@@ -9099,6 +9779,9 @@
       <c r="T16" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="V16" s="1" t="n">
+        <v>2</v>
+      </c>
       <c r="XDM16" s="2"/>
       <c r="XDN16" s="2"/>
       <c r="XDO16" s="2"/>
@@ -9191,6 +9874,9 @@
       </c>
       <c r="T17" s="1" t="n">
         <v>9</v>
+      </c>
+      <c r="V17" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="XDM17" s="2"/>
       <c r="XDN17" s="2"/>
@@ -9440,6 +10126,9 @@
       <c r="T19" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="V19" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="AKR19" s="1"/>
       <c r="AKS19" s="1"/>
       <c r="AKT19" s="1"/>
@@ -9592,6 +10281,9 @@
       <c r="T20" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="V20" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="XDM20" s="2"/>
       <c r="XDN20" s="2"/>
       <c r="XDO20" s="2"/>
@@ -9687,6 +10379,9 @@
       <c r="T21" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="V21" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
@@ -9740,7 +10435,9 @@
         <v>6</v>
       </c>
       <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
+      <c r="V22" s="1" t="n">
+        <v>9</v>
+      </c>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
@@ -10853,7 +11550,9 @@
         <v>7</v>
       </c>
       <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
+      <c r="V23" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="W23" s="2"/>
       <c r="X23" s="2"/>
       <c r="Y23" s="2"/>
@@ -12097,43 +12796,43 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12378,16 +13077,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13100,7 +13799,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13428,16 +14127,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13884,16 +14583,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14314,7 +15013,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14642,7 +15341,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
